--- a/artfynd/A 59993-2025 artfynd.xlsx
+++ b/artfynd/A 59993-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121335149</v>
+        <v>136830597</v>
       </c>
       <c r="B2" t="n">
-        <v>99096</v>
+        <v>93083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Harnäs, Upl</t>
+          <t>Stenvreten, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>630432</v>
+        <v>630191</v>
       </c>
       <c r="R2" t="n">
-        <v>6725435</v>
+        <v>6725115</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-01-08</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-01-08</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,79 +761,77 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Mika Thunell</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sanna Pousar</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sanna Pousar</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>JPN0076 Najaderna</t>
-        </is>
-      </c>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121335149</t>
+          <t>https://artportalen.se/Sighting/136830597</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121335150</v>
+        <v>136830697</v>
       </c>
       <c r="B3" t="n">
-        <v>99096</v>
+        <v>93447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Harnäs, Upl</t>
+          <t>Stenvreten, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>630416</v>
+        <v>630194</v>
       </c>
       <c r="R3" t="n">
-        <v>6725438</v>
+        <v>6725142</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,12 +858,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-01-08</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-01-08</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,39 +872,31 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Mika Thunell</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sanna Pousar</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sanna Pousar</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>JPN0076 Najaderna</t>
-        </is>
-      </c>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121335150</t>
+          <t>https://artportalen.se/Sighting/136830697</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121335151</v>
+        <v>121335149</v>
       </c>
       <c r="B4" t="n">
         <v>99096</v>
@@ -940,7 +926,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -949,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>630382</v>
+        <v>630432</v>
       </c>
       <c r="R4" t="n">
-        <v>6725448</v>
+        <v>6725435</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,13 +1005,13 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121335151</t>
+          <t>https://artportalen.se/Sighting/121335149</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121335152</v>
+        <v>121335150</v>
       </c>
       <c r="B5" t="n">
         <v>99096</v>
@@ -1055,7 +1041,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1064,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>630377</v>
+        <v>630416</v>
       </c>
       <c r="R5" t="n">
-        <v>6725449</v>
+        <v>6725438</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1134,13 +1120,13 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121335152</t>
+          <t>https://artportalen.se/Sighting/121335150</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121335153</v>
+        <v>121335151</v>
       </c>
       <c r="B6" t="n">
         <v>99096</v>
@@ -1170,7 +1156,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1179,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>630367</v>
+        <v>630382</v>
       </c>
       <c r="R6" t="n">
-        <v>6725450</v>
+        <v>6725448</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1249,13 +1235,13 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121335153</t>
+          <t>https://artportalen.se/Sighting/121335151</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121335154</v>
+        <v>121335152</v>
       </c>
       <c r="B7" t="n">
         <v>99096</v>
@@ -1285,7 +1271,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1294,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>630336</v>
+        <v>630377</v>
       </c>
       <c r="R7" t="n">
-        <v>6725456</v>
+        <v>6725449</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1364,13 +1350,13 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121335154</t>
+          <t>https://artportalen.se/Sighting/121335152</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121335155</v>
+        <v>121335153</v>
       </c>
       <c r="B8" t="n">
         <v>99096</v>
@@ -1400,7 +1386,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1409,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>630335</v>
+        <v>630367</v>
       </c>
       <c r="R8" t="n">
-        <v>6725457</v>
+        <v>6725450</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1479,13 +1465,13 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121335155</t>
+          <t>https://artportalen.se/Sighting/121335153</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121335156</v>
+        <v>121335154</v>
       </c>
       <c r="B9" t="n">
         <v>99096</v>
@@ -1515,7 +1501,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1524,10 +1510,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630326</v>
+        <v>630336</v>
       </c>
       <c r="R9" t="n">
-        <v>6725461</v>
+        <v>6725456</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1594,13 +1580,13 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121335156</t>
+          <t>https://artportalen.se/Sighting/121335154</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121335157</v>
+        <v>121335155</v>
       </c>
       <c r="B10" t="n">
         <v>99096</v>
@@ -1630,7 +1616,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1639,10 +1625,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>630244</v>
+        <v>630335</v>
       </c>
       <c r="R10" t="n">
-        <v>6725475</v>
+        <v>6725457</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1709,13 +1695,13 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121335157</t>
+          <t>https://artportalen.se/Sighting/121335155</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121335158</v>
+        <v>121335156</v>
       </c>
       <c r="B11" t="n">
         <v>99096</v>
@@ -1754,10 +1740,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>630214</v>
+        <v>630326</v>
       </c>
       <c r="R11" t="n">
-        <v>6725482</v>
+        <v>6725461</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1824,13 +1810,13 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121335158</t>
+          <t>https://artportalen.se/Sighting/121335156</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121335159</v>
+        <v>121335157</v>
       </c>
       <c r="B12" t="n">
         <v>99096</v>
@@ -1860,7 +1846,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1869,10 +1855,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>630216</v>
+        <v>630244</v>
       </c>
       <c r="R12" t="n">
-        <v>6725478</v>
+        <v>6725475</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1939,7 +1925,339 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/121335157</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121335158</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Harnäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>630214</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6725482</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-01-08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-01-08</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>JPN0076 Najaderna</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121335158</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121335159</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Harnäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>630216</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6725478</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-01-08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-01-08</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>JPN0076 Najaderna</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/121335159</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136830633</v>
+      </c>
+      <c r="B15" t="n">
+        <v>102479</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stenvreten, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>630212</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6725111</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136830633</t>
         </is>
       </c>
     </row>
@@ -1956,6 +2274,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59993-2025 artfynd.xlsx
+++ b/artfynd/A 59993-2025 artfynd.xlsx
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>630194</v>
+        <v>630189</v>
       </c>
       <c r="R3" t="n">
-        <v>6725142</v>
+        <v>6725131</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 59993-2025 artfynd.xlsx
+++ b/artfynd/A 59993-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830597</v>
       </c>
       <c r="B2" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136830697</v>
       </c>
       <c r="B3" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136830633</v>
       </c>
       <c r="B15" t="n">
-        <v>102479</v>
+        <v>102485</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 59993-2025 artfynd.xlsx
+++ b/artfynd/A 59993-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830597</v>
       </c>
       <c r="B2" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136830697</v>
       </c>
       <c r="B3" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136830633</v>
       </c>
       <c r="B15" t="n">
-        <v>102485</v>
+        <v>102487</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 59993-2025 artfynd.xlsx
+++ b/artfynd/A 59993-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830597</v>
       </c>
       <c r="B2" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136830697</v>
       </c>
       <c r="B3" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136830633</v>
       </c>
       <c r="B15" t="n">
-        <v>102487</v>
+        <v>102488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 59993-2025 artfynd.xlsx
+++ b/artfynd/A 59993-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830597</v>
       </c>
       <c r="B2" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136830697</v>
       </c>
       <c r="B3" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136830633</v>
       </c>
       <c r="B15" t="n">
-        <v>102488</v>
+        <v>102494</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 59993-2025 artfynd.xlsx
+++ b/artfynd/A 59993-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830597</v>
       </c>
       <c r="B2" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136830697</v>
       </c>
       <c r="B3" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136830633</v>
       </c>
       <c r="B15" t="n">
-        <v>102494</v>
+        <v>102498</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 59993-2025 artfynd.xlsx
+++ b/artfynd/A 59993-2025 artfynd.xlsx
@@ -2164,7 +2164,7 @@
         <v>136830633</v>
       </c>
       <c r="B15" t="n">
-        <v>102498</v>
+        <v>102500</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 59993-2025 artfynd.xlsx
+++ b/artfynd/A 59993-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830597</v>
       </c>
       <c r="B2" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136830697</v>
       </c>
       <c r="B3" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136830633</v>
       </c>
       <c r="B15" t="n">
-        <v>102500</v>
+        <v>102502</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 59993-2025 artfynd.xlsx
+++ b/artfynd/A 59993-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830597</v>
       </c>
       <c r="B2" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136830697</v>
       </c>
       <c r="B3" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136830633</v>
       </c>
       <c r="B15" t="n">
-        <v>102502</v>
+        <v>102515</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 59993-2025 artfynd.xlsx
+++ b/artfynd/A 59993-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830597</v>
       </c>
       <c r="B2" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136830697</v>
       </c>
       <c r="B3" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136830633</v>
       </c>
       <c r="B15" t="n">
-        <v>102515</v>
+        <v>102517</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 59993-2025 artfynd.xlsx
+++ b/artfynd/A 59993-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830597</v>
       </c>
       <c r="B2" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136830697</v>
       </c>
       <c r="B3" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136830633</v>
       </c>
       <c r="B15" t="n">
-        <v>102517</v>
+        <v>102520</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 59993-2025 artfynd.xlsx
+++ b/artfynd/A 59993-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830597</v>
       </c>
       <c r="B2" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136830697</v>
       </c>
       <c r="B3" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136830633</v>
       </c>
       <c r="B15" t="n">
-        <v>102520</v>
+        <v>102535</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 59993-2025 artfynd.xlsx
+++ b/artfynd/A 59993-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830597</v>
       </c>
       <c r="B2" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136830697</v>
       </c>
       <c r="B3" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136830633</v>
       </c>
       <c r="B15" t="n">
-        <v>102535</v>
+        <v>102536</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 59993-2025 artfynd.xlsx
+++ b/artfynd/A 59993-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830597</v>
       </c>
       <c r="B2" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136830697</v>
       </c>
       <c r="B3" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136830633</v>
       </c>
       <c r="B15" t="n">
-        <v>102536</v>
+        <v>102541</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 59993-2025 artfynd.xlsx
+++ b/artfynd/A 59993-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830597</v>
       </c>
       <c r="B2" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136830697</v>
       </c>
       <c r="B3" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136830633</v>
       </c>
       <c r="B15" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 59993-2025 artfynd.xlsx
+++ b/artfynd/A 59993-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830597</v>
       </c>
       <c r="B2" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136830697</v>
       </c>
       <c r="B3" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136830633</v>
       </c>
       <c r="B15" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 59993-2025 artfynd.xlsx
+++ b/artfynd/A 59993-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136830597</v>
       </c>
       <c r="B2" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136830697</v>
       </c>
       <c r="B3" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136830633</v>
       </c>
       <c r="B15" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 59993-2025 artfynd.xlsx
+++ b/artfynd/A 59993-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136830697</v>
       </c>
       <c r="B3" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59993-2025 artfynd.xlsx
+++ b/artfynd/A 59993-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136830697</v>
       </c>
       <c r="B3" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
